--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepRelDeal001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepRelDeal001.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25629"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\yunying\nanying\code-01\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\NYXP\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF00F02-C858-41C0-B2EB-D7980F233018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19460" windowHeight="7710"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -81,7 +82,10 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -128,7 +132,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -137,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -441,25 +451,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N1"/>
-  <sheetFormatPr defaultColWidth="15.36328125" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="15.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="1" max="1" width="18.77734375" customWidth="1"/>
     <col min="2" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="41.81640625" customWidth="1"/>
-    <col min="5" max="5" width="36.08984375" customWidth="1"/>
-    <col min="6" max="6" width="38.453125" customWidth="1"/>
-    <col min="7" max="7" width="33.90625" customWidth="1"/>
-    <col min="8" max="8" width="21.36328125" customWidth="1"/>
-    <col min="9" max="9" width="18.453125" customWidth="1"/>
-    <col min="10" max="10" width="23.08984375" customWidth="1"/>
-    <col min="11" max="11" width="23.1796875" customWidth="1"/>
-    <col min="12" max="12" width="28.6328125" customWidth="1"/>
-    <col min="13" max="13" width="29.36328125" customWidth="1"/>
+    <col min="4" max="4" width="41.77734375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="36.109375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="38.44140625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="33.88671875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="21.33203125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="18.44140625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="23.109375" style="4" customWidth="1"/>
+    <col min="11" max="11" width="23.21875" customWidth="1"/>
+    <col min="12" max="12" width="28.6640625" customWidth="1"/>
+    <col min="13" max="13" width="29.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" ht="44" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="2" customFormat="1" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -469,25 +479,25 @@
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -511,9 +521,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -522,9 +532,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepRelDeal001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepRelDeal001.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25629"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\NYXP\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF00F02-C858-41C0-B2EB-D7980F233018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="30930" windowHeight="16890"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,9 +27,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>产品名称</t>
-  </si>
-  <si>
     <t>更新时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -76,13 +72,17 @@
   </si>
   <si>
     <t>产品主代码</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品全称</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
@@ -451,66 +451,66 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N1"/>
-  <sheetFormatPr defaultColWidth="15.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="15.375" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="18.77734375" customWidth="1"/>
+    <col min="1" max="1" width="18.75" customWidth="1"/>
     <col min="2" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="41.77734375" style="4" customWidth="1"/>
-    <col min="5" max="5" width="36.109375" style="4" customWidth="1"/>
-    <col min="6" max="6" width="38.44140625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="33.88671875" style="4" customWidth="1"/>
-    <col min="8" max="8" width="21.33203125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="18.44140625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="23.109375" style="4" customWidth="1"/>
-    <col min="11" max="11" width="23.21875" customWidth="1"/>
-    <col min="12" max="12" width="28.6640625" customWidth="1"/>
-    <col min="13" max="13" width="29.33203125" customWidth="1"/>
+    <col min="4" max="4" width="41.75" style="4" customWidth="1"/>
+    <col min="5" max="5" width="36.125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="38.5" style="4" customWidth="1"/>
+    <col min="7" max="7" width="33.875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="21.375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="18.5" style="4" customWidth="1"/>
+    <col min="10" max="10" width="23.125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="23.25" customWidth="1"/>
+    <col min="12" max="12" width="28.625" customWidth="1"/>
+    <col min="13" max="13" width="29.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="2" customFormat="1" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -521,9 +521,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -532,9 +532,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
